--- a/input/other/metadata_variables.xlsx
+++ b/input/other/metadata_variables.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -409,7 +409,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -473,7 +473,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>w01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>w01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -564,12 +564,15 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1=Sin estudios; 2=Básica incompleta; 3=Básica completa; 4=Media incompleta; 5=Media completa; 6=Técnica incompleta; 7=Técnica completa; 8=Universitaria incompleta; 9=Universitaria completa o más</t>
+          <t>1=Sin estudios; 2=Básica incompleta; 3=Básica completa; 
+             4=Media incompleta; 5=Media completa; 6=Técnica incompleta; 
+             7=Técnica completa; 8=Universitaria incompleta; 
+             9=Universitaria completa o más</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>w01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -581,91 +584,97 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>c15</t>
+          <t>f05_01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Política</t>
+          <t>Justificación violencia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Posicionamiento político en escala izquierda-derecha</t>
+          <t>Justificación de que algunas personas persigan y golpeen
+                 a un 'delincuente' que acaba de cometer un asalto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0=Extrema izquierda; 10=Extrema derecha; 11=Ninguno; 12=NS/NR</t>
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces; 
+             4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:4, 6:7)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Base para moderadores ideológicos</t>
+          <t>Variable Y (análisis exploratorio)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>c18_11</t>
+          <t>f05_02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tolerancia a violencia</t>
+          <t>Justificación violencia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Justificación del uso de violencia física en el contexto de protestas y manifestaciones sociales</t>
+          <t>Justificación de que algunas personas amarren a un poste
+                 y desnuden a un 'delincuente' que acaba de cometer un asalto</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1=Nunca justificado; 2=Pocas veces; 3=Algunas veces; 4=Muchas veces; 5=Siempre justificado</t>
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces; 
+             4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:4, 6:7)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Variable X principal (RI-CLPM)</t>
+          <t>Variable Y (análisis exploratorio)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f05_01</t>
+          <t>f05_03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Violencia/Protesta</t>
+          <t>Justificación violencia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Participación en manifestaciones o marchas (ver codebook ELSOC para texto exacto)</t>
+          <t>Justificación de que Carabineros use la fuerza para 
+                 reprimir una manifestación pacífica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0=No; 1=Sí</t>
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces; 
+             4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>w01-w04</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -677,59 +686,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f05_02</t>
+          <t>f05_04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Violencia/Protesta</t>
+          <t>Justificación violencia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Participación en barricadas o bloqueos de calles (ver codebook ELSOC para texto exacto)</t>
+          <t>Justificación de que Carabineros desaloje a la fuerza
+                 a los estudiantes de un liceo en toma</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0=No; 1=Sí</t>
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces;
+             4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>w01-w04</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Variable Y (análisis exploratorio)</t>
+          <t>Variable Y PRINCIPAL (RI-CLPM)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f05_03</t>
+          <t>f05_05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Violencia/Protesta</t>
+          <t>Justificación violencia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Participación en huelgas o paros (ver codebook ELSOC para texto exacto)</t>
+          <t>Justificación de que un marido abofetee a su mujer por
+                 una pelea que ella comenzó</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0=No; 1=Sí</t>
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces;
+             4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:4, 6:7)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -741,59 +754,64 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f05_04</t>
+          <t>f05_06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Violencia/Protesta</t>
+          <t>Justificación violencia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Participación en actos de violencia en el contexto de protestas (ver codebook ELSOC para texto exacto)</t>
+          <t>Justificación de que un grupo de trabajadores en huelga
+                 bloquee la calle con barricadas para exigir el cumplimiento
+                 de sus derechos laborales</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0=No; 1=Sí</t>
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces;
+             4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Variable Y PRINCIPAL (RI-CLPM)</t>
+          <t>Variable Y (análisis exploratorio)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>f05_05</t>
+          <t>f05_07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Violencia/Protesta</t>
+          <t>Justificación violencia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Participación en ocupaciones de edificios o tomas (ver codebook ELSOC para texto exacto)</t>
+          <t>Justificación de que estudiantes tiren piedras a Carabineros
+                 en una marcha por la educación del país</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0=No; 1=Sí</t>
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces; 
+             4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>w01-w04</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -805,27 +823,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>f05_06</t>
+          <t>f06_01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Violencia/Protesta</t>
+          <t>Actitud punitiva</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Daño a propiedad pública o privada en el contexto de protestas (ver codebook ELSOC para texto exacto)</t>
+          <t>Todos los asaltantes debieran cumplir condenas de cárcel,
+                 sin ninguna excepción</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0=No; 1=Sí</t>
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo; 
+             3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo;
+             5=Totalmente de acuerdo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>?</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -837,27 +858,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f05_07</t>
+          <t>f06_02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Violencia/Protesta</t>
+          <t>Actitud punitiva</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Agresión física a personas en el contexto de protestas (ver codebook ELSOC para texto exacto)</t>
+          <t>Los jueces debieran dar condenas mucho más largas 
+                 a quienes han cometido asaltos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0=No; 1=Sí</t>
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo; 
+             3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo;
+             5=Totalmente de acuerdo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>?</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -874,22 +898,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Participación política</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Participación política contenciosa - ítem 1 (ver codebook ELSOC para texto exacto)</t>
+          <t>Satisfacción con la seguridad del barrio donde reside</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Escala Likert o dicotómica (ver codebook)</t>
+          <t>1=Totalmente insatisfecho; 2=Insatisfecho; 
+             3=Ni satisfecho ni insatisfecho; 4=Satisfecho;
+             5=Totalmente satisfecho</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>w01-w04</t>
+          <t>c(1:4, 6)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -906,22 +932,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Participación política</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Participación política contenciosa - ítem 1 módulo t09 (ver codebook ELSOC para texto exacto)</t>
+          <t>Frecuencia de riñas o peleas callejeras en el barrio
+                 durante los últimos 12 meses</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Escala Likert o dicotómica (ver codebook)</t>
+          <t>1=Nunca; 2=Pocas veces; 3=Algunas veces; 4=Muchas veces;
+             5=Siempre</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -938,22 +966,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Participación política</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Participación política contenciosa - ítem 2 módulo t09 (ver codebook ELSOC para texto exacto)</t>
+          <t>Frecuencia de robos o asaltos a personas, 
+                 casas y/o vehículos en el barrio durante los últimos 12 meses</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Escala Likert o dicotómica (ver codebook)</t>
+          <t>1=Nunca; 2=Pocas veces; 3=Algunas veces; 4=Muchas veces;
+             5=Siempre</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -970,22 +1000,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Participación política</t>
+          <t>Territorio</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Participación política contenciosa - ítem 3 módulo t09 (ver codebook ELSOC para texto exacto)</t>
+          <t>Frecuencia de tráfico de drogas en el barrio durante los últimos 12 meses</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Escala Likert o dicotómica (ver codebook)</t>
+          <t>1=Nunca; 2=Pocas veces; 3=Algunas veces; 4=Muchas veces;
+             5=Siempre</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1007,7 +1038,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salario mensual percibido para el trabajador o profesional mejor remunerado en Chile (ej. gerente)</t>
+          <t>Salario mensual percibido para gerente</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1017,7 +1048,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1039,7 +1070,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salario mensual percibido para el trabajador peor remunerado en Chile (ej. obrero no calificado)</t>
+          <t>Salario mensual percibido para obrero</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1049,7 +1080,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1071,7 +1102,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Salario mensual justo para el trabajador o profesional mejor remunerado en Chile</t>
+          <t>Salario mensual justo para gerente</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1081,7 +1112,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1103,7 +1134,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Salario mensual justo para el trabajador peor remunerado en Chile</t>
+          <t>Salario mensual justo para obrero</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1113,7 +1144,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1125,222 +1156,303 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>d02_01</t>
+          <t>brecha_perc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Justicia distributiva</t>
+          <t>Desigualdad (creada)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Percepción de justicia en el sistema de pensiones en Chile</t>
+          <t>Brecha salarial percibida.
+                 Valores positivos indican mayor desigualdad percibida.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1=Completamente injusto; 5=Completamente justo</t>
+          <t>Numérico continuo (log-ratio)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>w01-w04</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Variable X (análisis exploratorio)</t>
+          <t>Variable X (RI-CLPM)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>d02_02</t>
+          <t>brecha_just</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Justicia distributiva</t>
+          <t>Desigualdad (creada)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Percepción de justicia en el sistema de educación en Chile</t>
+          <t>Brecha salarial justa.+
+                 Valores positivos indican mayor tolerancia a la desigualdad.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1=Completamente injusto; 5=Completamente justo</t>
+          <t>Numérico continuo (log-ratio)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>w01-w04</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Variable X (análisis exploratorio)</t>
+          <t>Variable X (RI-CLPM)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>d02_03</t>
+          <t>c18_11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Justicia distributiva</t>
+          <t>Tolerancia a la desigualdad</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Percepción de justicia en el sistema de salud en Chile</t>
+          <t>En Chile, las diferencias de ingreso son demasiado grandes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1=Completamente injusto; 5=Completamente justo</t>
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo; 
+             3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo; 
+             5=Totalmente de acuerdo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>w01-w04</t>
+          <t>c(1:7)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Variable X (análisis exploratorio)</t>
+          <t>Variable X principal (RI-CLPM)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>brecha_perc</t>
+          <t>d02_01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Desigualdad (creada)</t>
+          <t>Justicia distributiva</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brecha salarial percibida: logaritmo natural de la razón entre el salario percibido del mejor y peor pagado. Calculada en cada ola como log(d03_01 / d03_02). Valores positivos indican mayor desigualdad percibida.</t>
+          <t>Es justo que las personas de altos ingresos tengan mejores
+                 pensiones que las personas con ingresos más bajos</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Numérico continuo (log-ratio)</t>
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo; 
+             3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo;
+             5=Totalmente de acuerdo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:4)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Variable X (RI-CLPM)</t>
+          <t>Variable X (análisis exploratorio)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>brecha_just</t>
+          <t>d02_02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Desigualdad (creada)</t>
+          <t>Justicia distributiva</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brecha salarial justa: logaritmo natural de la razón entre el salario justo del mejor y peor pagado. Calculada en cada ola como log(d04_01 / d04_02). Valores positivos indican mayor tolerancia a la desigualdad.</t>
+          <t>Es justo que las personas de altos ingresos tengan una mejor
+                 educación para sus hijos que las personas con ingresos más bajos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Numérico continuo (log-ratio)</t>
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo;
+             3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo;
+             5=Totalmente de acuerdo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>w01-w07</t>
+          <t>c(1:4)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Variable X (RI-CLPM)</t>
+          <t>Variable X (análisis exploratorio)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ideol4</t>
+          <t>d02_03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Política (creada)</t>
+          <t>Justicia distributiva</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ideología política del encuestado en cuatro categorías, creada a partir de c15_w01</t>
+          <t>Es justo que las personas de altos ingresos puedan acceder a una
+                 mejor atención de salud que las personas con ingresos más bajos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1=Izquierda (c15: 0-3); 2=Centro (c15: 4-6); 3=Derecha (c15: 7-10); 4=Ninguno/NS/NR (c15: 11-12)</t>
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo;
+             3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo;
+             5=Totalmente de acuerdo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>w01 (time-invariant)</t>
+          <t>c(1:4)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Moderador</t>
+          <t>Variable X (análisis exploratorio)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>c15</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Política</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Posicionamiento político en escala izquierda-derecha</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0=Izquierda; 5=Centro; 10=Derecha; 11=Ninguno; 12=NS/NR</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>c(1:7)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Base para moderadores ideológicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ideol4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Política (creada)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ideología política del encuestado en cuatro categorías,
+                 creada a partir de c15_w01</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1=Izquierda (c15: 0-3); 2=Centro (c15: 4-6); 3=Derecha (c15: 7-10);}
+             4=Ninguno/NS/NR (c15: 11-12)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>w01 (time-invariant)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Moderador</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>ideol2</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>Política (creada)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ideología política del encuestado como variable binaria: si se posiciona o no en el espectro político, creada a partir de c15_w01</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ideología política del encuestado como variable binaria:
+                 si se posiciona o no en el espectro político, creada a partir
+                 de c15_w01</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>0=No se posiciona (c15: 11-12); 1=Se posiciona (c15: 0-10)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>w01 (time-invariant)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Moderador</t>
         </is>

--- a/input/other/metadata_variables.xlsx
+++ b/input/other/metadata_variables.xlsx
@@ -564,9 +564,9 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1=Sin estudios; 2=Básica incompleta; 3=Básica completa; 
-             4=Media incompleta; 5=Media completa; 6=Técnica incompleta; 
-             7=Técnica completa; 8=Universitaria incompleta; 
+          <t>1=Sin estudios; 2=Básica incompleta; 3=Básica completa;
+             4=Media incompleta; 5=Media completa; 6=Técnica incompleta;
+             7=Técnica completa; 8=Universitaria incompleta;
              9=Universitaria completa o más</t>
         </is>
       </c>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces; 
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces;
              4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
@@ -634,7 +634,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces; 
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces;
              4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
@@ -662,13 +662,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Justificación de que Carabineros use la fuerza para 
+          <t>Justificación de que Carabineros use la fuerza para
                  reprimir una manifestación pacífica</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces; 
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces;
              4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
@@ -805,7 +805,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces; 
+          <t>1=Nunca se justifica; 2=Pocas veces; 3=Algunas veces;
              4=Muchas veces; 5=Siempre se justifica</t>
         </is>
       </c>
@@ -839,7 +839,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1=Totalmente en desacuerdo; 2=En desacuerdo; 
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo;
              3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo;
              5=Totalmente de acuerdo</t>
         </is>
@@ -868,13 +868,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los jueces debieran dar condenas mucho más largas 
+          <t>Los jueces debieran dar condenas mucho más largas
                  a quienes han cometido asaltos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1=Totalmente en desacuerdo; 2=En desacuerdo; 
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo;
              3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo;
              5=Totalmente de acuerdo</t>
         </is>
@@ -908,7 +908,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1=Totalmente insatisfecho; 2=Insatisfecho; 
+          <t>1=Totalmente insatisfecho; 2=Insatisfecho;
              3=Ni satisfecho ni insatisfecho; 4=Satisfecho;
              5=Totalmente satisfecho</t>
         </is>
@@ -971,7 +971,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Frecuencia de robos o asaltos a personas, 
+          <t>Frecuencia de robos o asaltos a personas,
                  casas y/o vehículos en el barrio durante los últimos 12 meses</t>
         </is>
       </c>
@@ -1237,8 +1237,8 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1=Totalmente en desacuerdo; 2=En desacuerdo; 
-             3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo; 
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo;
+             3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo;
              5=Totalmente de acuerdo</t>
         </is>
       </c>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1=Totalmente en desacuerdo; 2=En desacuerdo; 
+          <t>1=Totalmente en desacuerdo; 2=En desacuerdo;
              3=Ni de acuerdo ni en desacuerdo; 4=De acuerdo;
              5=Totalmente de acuerdo</t>
         </is>

--- a/input/other/metadata_variables.xlsx
+++ b/input/other/metadata_variables.xlsx
@@ -394,7 +394,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Identificador</t>
+          <t>Encuesta</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -426,7 +426,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Identificador</t>
+          <t>Encuesta</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -458,7 +458,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Identificador</t>
+          <t>Encuesta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sociodemográfica</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sociodemográfica</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sociodemográfica</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Justificación violencia</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Justificación violencia</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Justificación violencia</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Justificación violencia</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Justificación violencia</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Justificación violencia</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Justificación violencia</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Actitud punitiva</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>c(1:4, 6:7)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Actitud punitiva</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>c(1:4, 6:7)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Territorio</t>
+          <t>Dependiente</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Desigualdad</t>
+          <t>Insumo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Desigualdad</t>
+          <t>Insumo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Desigualdad</t>
+          <t>Insumo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Desigualdad</t>
+          <t>Insumo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Desigualdad (creada)</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Desigualdad (creada)</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tolerancia a la desigualdad</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Justicia distributiva</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Justicia distributiva</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Justicia distributiva</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Política</t>
+          <t>Insumo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Política (creada)</t>
+          <t>Moderador</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>w01 (time-invariant)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Política (creada)</t>
+          <t>Moderador</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>w01 (time-invariant)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
